--- a/data/gravel/Sanitas Tap Root 2025.xlsx
+++ b/data/gravel/Sanitas Tap Root 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDDB14B-55D8-DF44-824B-4BBD78AAB822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE86467F-5B99-774F-A597-6FC373E2E3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41880" yWindow="-28300" windowWidth="26080" windowHeight="25080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17420" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -357,6 +357,12 @@
   </si>
   <si>
     <t>https://www.sanitasbikes.com/tap-root-titanium-hardtail</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Durango, Colorado, USA</t>
   </si>
 </sst>
 </file>
@@ -764,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V73"/>
+  <dimension ref="A1:V74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -1886,6 +1892,14 @@
         <v>83</v>
       </c>
     </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Sanitas Tap Root 2025.xlsx
+++ b/data/gravel/Sanitas Tap Root 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE86467F-5B99-774F-A597-6FC373E2E3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3536D83-6203-E643-B289-A26041E3155F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17420" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1778,6 +1778,9 @@
       <c r="A54" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="B54" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">

--- a/data/gravel/Sanitas Tap Root 2025.xlsx
+++ b/data/gravel/Sanitas Tap Root 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3536D83-6203-E643-B289-A26041E3155F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC4F7C5-D3AB-7E4C-85E8-B5836285520F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -363,6 +363,24 @@
   </si>
   <si>
     <t>Durango, Colorado, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -770,7 +788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V74"/>
+  <dimension ref="A1:V80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -1747,159 +1765,189 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" s="2">
-        <v>31.6</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B54" s="2">
-        <v>36</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B58" s="2">
+        <v>31.6</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>81</v>
+        <v>48</v>
+      </c>
+      <c r="B60" s="2">
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B63" s="2">
-        <v>2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B64" s="2">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="B69" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B70" s="2">
-        <v>2950</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76" s="2">
+        <v>2950</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B80" s="2" t="s">
         <v>109</v>
       </c>
     </row>

--- a/data/gravel/Sanitas Tap Root 2025.xlsx
+++ b/data/gravel/Sanitas Tap Root 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC4F7C5-D3AB-7E4C-85E8-B5836285520F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8056F797-0FF0-9B4E-B89D-5D24E2AA4AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7720" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1726,7 +1726,7 @@
         <v>38</v>
       </c>
       <c r="B44" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
@@ -1734,7 +1734,7 @@
         <v>39</v>
       </c>
       <c r="B45" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">

--- a/data/gravel/Sanitas Tap Root 2025.xlsx
+++ b/data/gravel/Sanitas Tap Root 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8056F797-0FF0-9B4E-B89D-5D24E2AA4AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A904AE3-D621-2542-B813-41732D22E08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7720" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -254,9 +254,6 @@
     <t>front_center</t>
   </si>
   <si>
-    <t>trail</t>
-  </si>
-  <si>
     <t>Sanitas</t>
   </si>
   <si>
@@ -381,6 +378,12 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>120-130</t>
   </si>
 </sst>
 </file>
@@ -804,7 +807,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
@@ -812,7 +815,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -836,12 +839,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -849,7 +852,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="22" x14ac:dyDescent="0.3">
@@ -857,25 +860,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="E8" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="H8" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>76</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
@@ -897,7 +900,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C9" s="12">
         <v>578</v>
@@ -935,7 +938,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" s="12">
         <v>66.5</v>
@@ -973,7 +976,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" s="12">
         <v>74.5</v>
@@ -1011,7 +1014,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C12" s="12">
         <v>356</v>
@@ -1049,7 +1052,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C13" s="12">
         <v>90</v>
@@ -1086,7 +1089,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C14" s="12">
         <v>430</v>
@@ -1124,7 +1127,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C15" s="12">
         <v>57.5</v>
@@ -1162,7 +1165,7 @@
         <v>18</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16" s="12">
         <v>780</v>
@@ -1200,7 +1203,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C17" s="12">
         <v>425</v>
@@ -1238,7 +1241,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C18" s="12">
         <v>594</v>
@@ -1274,10 +1277,10 @@
     </row>
     <row r="19" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C19" s="12">
         <v>130</v>
@@ -1357,7 +1360,7 @@
         <v>540</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
@@ -1395,7 +1398,7 @@
         <v>44</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
@@ -1411,7 +1414,7 @@
     </row>
     <row r="23" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="8"/>
@@ -1603,7 +1606,7 @@
         <v>2.4</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.3">
@@ -1668,7 +1671,7 @@
         <v>68</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -1676,7 +1679,7 @@
         <v>69</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -1684,7 +1687,7 @@
         <v>70</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -1692,7 +1695,7 @@
         <v>33</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -1725,8 +1728,8 @@
       <c r="A44" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="2">
-        <v>120</v>
+      <c r="B44" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
@@ -1765,32 +1768,32 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -1798,7 +1801,7 @@
         <v>44</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -1855,7 +1858,7 @@
         <v>53</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -1863,7 +1866,7 @@
         <v>54</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
@@ -1940,15 +1943,15 @@
         <v>67</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Sanitas Tap Root 2025.xlsx
+++ b/data/gravel/Sanitas Tap Root 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A904AE3-D621-2542-B813-41732D22E08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BB5486-2E2C-0340-B4D5-A2EADBFF6047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1737,7 +1737,7 @@
         <v>39</v>
       </c>
       <c r="B45" s="2">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
